--- a/output/merged_output.xlsx
+++ b/output/merged_output.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +54,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,330 +437,337 @@
   </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Anita</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>52000</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>John</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>950</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Vikram</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>1300</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Sara</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Webcam</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>3200</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Neha</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>14800</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>John</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>David</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>900</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sara</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Chennai</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Rahul</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>8500</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Rahul</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>51000</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>David</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Anita</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>8700</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>920</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Kiran</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Visakhapatnam</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/merged_output.xlsx
+++ b/output/merged_output.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$16</definedName>
@@ -770,4 +771,77 @@
   <autoFilter ref="A1:D16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Excel Automation Toolkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REport</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Rows</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Duplicate Rows Removed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Blank Rows Removed</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Final Rows</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/merged_output.xlsx
+++ b/output/merged_output.xlsx
@@ -147,6 +147,140 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cleaning Report</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Summary'!$A$4:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$B$4:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Metrics</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -442,7 +576,7 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,7 +897,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Visakapatnam</t>
         </is>
       </c>
     </row>
@@ -843,5 +977,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>